--- a/Assets/GameResource/Excel/兵种表.xlsx
+++ b/Assets/GameResource/Excel/兵种表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D02B87A-F76B-43F8-A20A-88007216EA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A275EF04-0837-473C-B8E1-A77ABC06B2B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="88">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -170,11 +170,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>词条表关联
-多个用逗号隔开</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>渴血者</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,10 +218,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>造成5AOE伤害，获得一回合反击，概率30%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>刺客</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -254,22 +245,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>造成4伤害，其他目标造成1点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成5伤害，其他目标造成1点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成5伤害，其他目标造成2点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成6伤害，其他目标造成4点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>造成3伤害，连击1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -290,11 +265,110 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>魔导师</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>术士</t>
+    <t>造成5群体伤害，获得一回合反击，概率30%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择目标造成4伤害，其他目标造成1伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择目标造成5伤害，其他目标造成1伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择目标造成5伤害，其他目标造成2伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择目标造成6伤害，其他目标造成4伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贤者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学徒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成3法术伤害x次，敌人每次受到伤害20%概率获得迟缓*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成3法术伤害x次，敌人每次受到伤害30%概率获得迟缓*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成4法术伤害x次，敌人每次受到伤害30%概率获得迟缓*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成5法术伤害x次，敌人每次受到伤害50%概率获得迟缓*1，每次命中迟缓的敌人，会造成双倍伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小偷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盗墓贼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>走私者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侠盗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20%概率盗窃目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10%概率盗窃目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15%概率盗窃目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25%概率盗窃目标，有1%的概率盗窃到神器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大魔法师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人像刺客</t>
+  </si>
+  <si>
+    <t>人像剑圣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人像法师</t>
+  </si>
+  <si>
+    <t>人像侠盗</t>
+  </si>
+  <si>
+    <t>人像牧师</t>
+  </si>
+  <si>
+    <t>人像疫医</t>
+  </si>
+  <si>
+    <t>词条表关联</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -623,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.88671875" customWidth="1"/>
@@ -677,10 +751,10 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -700,7 +774,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -720,7 +794,7 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -743,7 +817,7 @@
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -766,7 +840,7 @@
         <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -789,7 +863,7 @@
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -812,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -832,7 +906,7 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -852,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -872,7 +946,7 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -888,6 +962,9 @@
       <c r="D12">
         <v>2</v>
       </c>
+      <c r="E12" t="s">
+        <v>85</v>
+      </c>
       <c r="F12" t="s">
         <v>30</v>
       </c>
@@ -908,6 +985,9 @@
       <c r="D13">
         <v>2</v>
       </c>
+      <c r="E13" t="s">
+        <v>85</v>
+      </c>
       <c r="F13" t="s">
         <v>33</v>
       </c>
@@ -928,6 +1008,9 @@
       <c r="D14">
         <v>2</v>
       </c>
+      <c r="E14" t="s">
+        <v>85</v>
+      </c>
       <c r="F14" t="s">
         <v>34</v>
       </c>
@@ -948,6 +1031,9 @@
       <c r="D15">
         <v>2</v>
       </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
       <c r="F15" t="s">
         <v>31</v>
       </c>
@@ -965,8 +1051,11 @@
       <c r="D16">
         <v>1</v>
       </c>
+      <c r="E16" t="s">
+        <v>82</v>
+      </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -980,13 +1069,16 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
+      <c r="E17" t="s">
+        <v>82</v>
+      </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G17">
         <v>3</v>
@@ -1000,13 +1092,16 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
+      <c r="E18" t="s">
+        <v>82</v>
+      </c>
       <c r="F18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G18">
         <v>3</v>
@@ -1025,8 +1120,11 @@
       <c r="D19">
         <v>1</v>
       </c>
+      <c r="E19" t="s">
+        <v>82</v>
+      </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -1040,13 +1138,16 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
+      <c r="E20" t="s">
+        <v>86</v>
+      </c>
       <c r="F20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G20">
         <v>4</v>
@@ -1060,13 +1161,16 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
+      <c r="E21" t="s">
+        <v>86</v>
+      </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G21">
         <v>4</v>
@@ -1085,8 +1189,11 @@
       <c r="D22">
         <v>1</v>
       </c>
+      <c r="E22" t="s">
+        <v>86</v>
+      </c>
       <c r="F22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G22">
         <v>4</v>
@@ -1100,13 +1207,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
+      <c r="E23" t="s">
+        <v>86</v>
+      </c>
       <c r="F23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G23">
         <v>4</v>
@@ -1120,13 +1230,16 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
+      <c r="E24" t="s">
+        <v>81</v>
+      </c>
       <c r="F24" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -1140,13 +1253,16 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
+      <c r="E25" t="s">
+        <v>81</v>
+      </c>
       <c r="F25" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -1160,13 +1276,16 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
+      <c r="E26" t="s">
+        <v>81</v>
+      </c>
       <c r="F26" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -1180,26 +1299,203 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
+      <c r="E27" t="s">
+        <v>81</v>
+      </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28">
+        <v>7</v>
+      </c>
       <c r="C28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28">
+        <v>-1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
-        <v>67</v>
+      <c r="D29">
+        <v>-1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30">
+        <v>-1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>7</v>
+      </c>
+      <c r="C31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31">
+        <v>-1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32">
+        <v>8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" t="s">
+        <v>78</v>
+      </c>
+      <c r="G33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
+        <v>84</v>
+      </c>
+      <c r="F35" t="s">
+        <v>79</v>
+      </c>
+      <c r="G35">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/GameResource/Excel/兵种表.xlsx
+++ b/Assets/GameResource/Excel/兵种表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A275EF04-0837-473C-B8E1-A77ABC06B2B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F727965-0ECD-4A57-A104-E63D3DB60866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -146,26 +146,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回复6生命，25%概率回春</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复12生命，40%概率回春，触发回春后赐福随机一名友方士兵，使其下次攻击免除能量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>狼人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回复6生命，30%概率回春，下回合恢复等量生命</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复10生命，30%概率回春，下回合恢复等量生命</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EntryId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -190,34 +174,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>造成5单体伤害，吸血1，渴血</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成6单体伤害，吸血1，渴血</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成6单体伤害，吸血2，渴血</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吸血2，攻击造成7点伤害，渴血解除攻击目标限制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成3伤害，获得一回合反击，概率10%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成3伤害，获得一回合反击，概率20%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成4伤害，获得一回合反击，概率25%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>刺客</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -229,62 +185,10 @@
     <t>夜刃</t>
   </si>
   <si>
-    <t>造成3伤害，获得1层坚韧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成4伤害，获得1层坚韧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成4伤害，获得2层坚韧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成6伤害，获得2层坚韧，触发坚韧时移除1个随机负面效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成3伤害，连击1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成3伤害，连击2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>夜行者</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>造成4伤害，连击2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成4伤害，连击3，击杀敌人返还使用能量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成5群体伤害，获得一回合反击，概率30%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择目标造成4伤害，其他目标造成1伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择目标造成5伤害，其他目标造成1伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择目标造成5伤害，其他目标造成2伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择目标造成6伤害，其他目标造成4伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>贤者</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -297,22 +201,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>造成3法术伤害x次，敌人每次受到伤害20%概率获得迟缓*1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成3法术伤害x次，敌人每次受到伤害30%概率获得迟缓*1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成4法术伤害x次，敌人每次受到伤害30%概率获得迟缓*1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成5法术伤害x次，敌人每次受到伤害50%概率获得迟缓*1，每次命中迟缓的敌人，会造成双倍伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>小偷</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -341,10 +229,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>25%概率盗窃目标，有1%的概率盗窃到神器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>大魔法师</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -369,6 +253,122 @@
   </si>
   <si>
     <t>词条表关联</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成3伤害\n获得1层坚韧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成4伤害\n获得1层坚韧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成3法术伤害x次\n敌人每次受到伤害20%概率获得迟缓*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成3法术伤害x次\n敌人每次受到伤害30%概率获得迟缓*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成4法术伤害x次\n敌人每次受到伤害30%概率获得迟缓*1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成5法术伤害x次\n敌人每次受到伤害50%概率获得迟缓*1，每次命中迟缓的敌人，会造成双倍伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25%概率盗窃目标\n有1%的概率盗窃到神器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成4伤害\n获得2层坚韧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标造成4伤害\n其他造成1伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标造成5伤害\n其他造成1伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标造成5伤害\n其他造成2伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标造成6伤害\n其他造成4伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成6伤害\n获得2层坚韧\n触发坚韧时移除1个随机负面效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复6生命\n25%概率回春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复6生命\n30%概率回春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复10生命\n30%概率回春</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复12生命\n40%概率回春\n赐福随机一名友方士兵使其下次攻击免除能量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成3伤害\n获得一回合反击\n触发概率10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成3伤害\n获得一回合反击\n触发概率20%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成4伤害\n获得一回合反击\n触发概率25%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成5群体伤害\n获得一回合反击\n触发概率30%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成5伤害1吸血\n渴血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成6伤害1吸血\n渴血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成6伤害2吸血\n渴血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成7伤害2吸血x\n渴血解除攻击目标限制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成3伤害\n连击1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成3伤害\n连击2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成4伤害\n连击2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成4伤害\n连击3\n击杀敌人返还使用能量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -728,7 +728,7 @@
         <v>10</v>
       </c>
       <c r="G1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -774,7 +774,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -794,7 +794,7 @@
         <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -817,7 +817,7 @@
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -840,7 +840,7 @@
         <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -863,7 +863,7 @@
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -906,7 +906,7 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -946,7 +946,7 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -963,10 +963,10 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -986,10 +986,10 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1009,10 +1009,10 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1032,10 +1032,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1052,10 +1052,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -1069,16 +1069,16 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="G17">
         <v>3</v>
@@ -1092,16 +1092,16 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G18">
         <v>3</v>
@@ -1121,10 +1121,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -1138,16 +1138,16 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <v>4</v>
@@ -1161,16 +1161,16 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="G21">
         <v>4</v>
@@ -1184,16 +1184,16 @@
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="G22">
         <v>4</v>
@@ -1207,16 +1207,16 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="G23">
         <v>4</v>
@@ -1230,16 +1230,16 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -1253,16 +1253,16 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -1276,16 +1276,16 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -1299,16 +1299,16 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -1322,16 +1322,16 @@
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="D28">
         <v>-1</v>
       </c>
       <c r="E28" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="F28" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G28">
         <v>6</v>
@@ -1345,16 +1345,16 @@
         <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D29">
         <v>-1</v>
       </c>
       <c r="E29" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="F29" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G29">
         <v>6</v>
@@ -1368,16 +1368,16 @@
         <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D30">
         <v>-1</v>
       </c>
       <c r="E30" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="F30" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G30">
         <v>6</v>
@@ -1391,16 +1391,16 @@
         <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D31">
         <v>-1</v>
       </c>
       <c r="E31" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="F31" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G31">
         <v>6</v>
@@ -1414,16 +1414,16 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F32" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="G32">
         <v>7</v>
@@ -1437,16 +1437,16 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="G33">
         <v>7</v>
@@ -1460,16 +1460,16 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F34" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="G34">
         <v>7</v>
@@ -1483,16 +1483,16 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F35" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="G35">
         <v>7</v>
